--- a/artfynd/A 14815-2025 artfynd.xlsx
+++ b/artfynd/A 14815-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1949,10 +1949,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115576757</v>
+        <v>115577084</v>
       </c>
       <c r="B12" t="n">
-        <v>99909</v>
+        <v>90951</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1965,31 +1965,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1997,13 +2000,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564661</v>
+        <v>564642</v>
       </c>
       <c r="R12" t="n">
-        <v>6619468</v>
+        <v>6619428</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2047,7 +2050,12 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Granstubbe, med klibbticka.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2065,10 +2073,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115577084</v>
+        <v>116462948</v>
       </c>
       <c r="B13" t="n">
-        <v>90951</v>
+        <v>91061</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2098,16 +2106,8 @@
           <t>(Fr.) Donk</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -2116,13 +2116,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564642</v>
+        <v>564661</v>
       </c>
       <c r="R13" t="n">
-        <v>6619428</v>
+        <v>6619468</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2146,12 +2146,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Granstubbe, med klibbticka.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2186,122 +2186,6 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>116462948</v>
-      </c>
-      <c r="B14" t="n">
-        <v>91061</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1339</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Brandticka</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Pycnoporellus fulgens</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Baståsen O, Vstm</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>564661</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6619468</v>
-      </c>
-      <c r="S14" t="n">
-        <v>25</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Sura</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2024-04-30</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2024-04-30</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
